--- a/Data_Kesesuaian.xlsx
+++ b/Data_Kesesuaian.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Muhammad Nabil\Dropbox\PC\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TA\Implementasi_Map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3FC003-2EB9-459C-A618-84481F6CEAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09A2713-499F-4246-A04A-84CF264E9994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{98B0522D-F215-483E-9EB2-9849649A00B1}"/>
+    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{98B0522D-F215-483E-9EB2-9849649A00B1}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet 1" sheetId="2" r:id="rId1"/>
@@ -6621,10 +6621,10 @@
         <v>27</v>
       </c>
       <c r="C116" s="28">
-        <v>-7.2555825</v>
+        <v>-7.7555825</v>
       </c>
       <c r="D116" s="28">
-        <v>-7.2555825</v>
+        <v>112.53453690000001</v>
       </c>
       <c r="E116" s="4">
         <v>93</v>
@@ -6816,7 +6816,7 @@
         <v>-7.7605025999999997</v>
       </c>
       <c r="D120" s="28">
-        <v>-7.7605025999999997</v>
+        <v>112.5283429</v>
       </c>
       <c r="E120" s="4">
         <v>46</v>

--- a/Data_Kesesuaian.xlsx
+++ b/Data_Kesesuaian.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TA\Implementasi_Map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09A2713-499F-4246-A04A-84CF264E9994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3E08AD-0C2B-4D98-BC3E-CD838EDEA479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{98B0522D-F215-483E-9EB2-9849649A00B1}"/>
+    <workbookView xWindow="-26880" yWindow="1920" windowWidth="22035" windowHeight="12960" xr2:uid="{98B0522D-F215-483E-9EB2-9849649A00B1}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet 1" sheetId="2" r:id="rId1"/>
@@ -527,6 +527,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -538,30 +562,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -974,10 +974,10 @@
       <c r="B2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="27">
         <v>-7.2106548999999998</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="30">
         <v>109.89419669999999</v>
       </c>
       <c r="E2" s="2">
@@ -1027,8 +1027,8 @@
       <c r="B3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
       <c r="E3" s="2">
         <v>41</v>
       </c>
@@ -1076,10 +1076,10 @@
       <c r="B4" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="27">
         <v>-7.2237650000000002</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="27">
         <v>109.8706483</v>
       </c>
       <c r="E4" s="2">
@@ -1129,8 +1129,8 @@
       <c r="B5" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
       <c r="E5" s="2">
         <v>118</v>
       </c>
@@ -1178,10 +1178,10 @@
       <c r="B6" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="27">
         <v>-7.2153450000000001</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="27">
         <v>109.8350167</v>
       </c>
       <c r="E6" s="2">
@@ -1231,8 +1231,8 @@
       <c r="B7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
       <c r="E7" s="2">
         <v>7</v>
       </c>
@@ -1280,10 +1280,10 @@
       <c r="B8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="27">
         <v>-7.1898422999999996</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="27">
         <v>109.8789974</v>
       </c>
       <c r="E8" s="2">
@@ -1331,8 +1331,8 @@
       <c r="B9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
       <c r="E9" s="2">
         <v>69</v>
       </c>
@@ -1378,8 +1378,8 @@
       <c r="B10" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
       <c r="E10" s="2">
         <v>41</v>
       </c>
@@ -1425,8 +1425,8 @@
       <c r="B11" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
       <c r="E11" s="2">
         <v>66</v>
       </c>
@@ -1472,10 +1472,10 @@
       <c r="B12" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="27">
         <v>-7.1903236000000001</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="27">
         <v>109.8794669</v>
       </c>
       <c r="E12" s="2">
@@ -1523,8 +1523,8 @@
       <c r="B13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
       <c r="E13" s="2">
         <v>92</v>
       </c>
@@ -1570,8 +1570,8 @@
       <c r="B14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
       <c r="E14" s="2">
         <v>76</v>
       </c>
@@ -1617,8 +1617,8 @@
       <c r="B15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
       <c r="E15" s="2">
         <v>78</v>
       </c>
@@ -1664,10 +1664,10 @@
       <c r="B16" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="27">
         <v>-7.1967181</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="27">
         <v>109.91201719999999</v>
       </c>
       <c r="E16" s="2">
@@ -1715,8 +1715,8 @@
       <c r="B17" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
       <c r="E17" s="2">
         <v>97</v>
       </c>
@@ -1762,8 +1762,8 @@
       <c r="B18" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
       <c r="E18" s="2">
         <v>61</v>
       </c>
@@ -1809,8 +1809,8 @@
       <c r="B19" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
       <c r="E19" s="2">
         <v>62</v>
       </c>
@@ -1856,10 +1856,10 @@
       <c r="B20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="27">
         <v>-7.2018072999999996</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="27">
         <v>109.91100179999999</v>
       </c>
       <c r="E20" s="2">
@@ -1907,8 +1907,8 @@
       <c r="B21" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
       <c r="E21" s="2">
         <v>153</v>
       </c>
@@ -1954,8 +1954,8 @@
       <c r="B22" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
       <c r="E22" s="2">
         <v>188</v>
       </c>
@@ -2001,8 +2001,8 @@
       <c r="B23" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
       <c r="E23" s="2">
         <v>123</v>
       </c>
@@ -2048,10 +2048,10 @@
       <c r="B24" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="27">
         <v>-7.2289748999999999</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="27">
         <v>109.9421655</v>
       </c>
       <c r="E24" s="2">
@@ -2101,8 +2101,8 @@
       <c r="B25" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
       <c r="E25" s="2">
         <v>47</v>
       </c>
@@ -2150,10 +2150,10 @@
       <c r="B26" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="27">
         <v>-7.2285385</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="27">
         <v>109.94195910000001</v>
       </c>
       <c r="E26" s="2">
@@ -2203,8 +2203,8 @@
       <c r="B27" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
       <c r="E27" s="2">
         <v>73</v>
       </c>
@@ -2252,10 +2252,10 @@
       <c r="B28" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="23">
+      <c r="C28" s="22">
         <v>-7.2279198999999998</v>
       </c>
-      <c r="D28" s="23">
+      <c r="D28" s="22">
         <v>109.9022739</v>
       </c>
       <c r="E28" s="2">
@@ -2305,8 +2305,8 @@
       <c r="B29" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
       <c r="E29" s="2">
         <v>71</v>
       </c>
@@ -2354,10 +2354,10 @@
       <c r="B30" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C30" s="23">
+      <c r="C30" s="22">
         <v>-7.2279198999999998</v>
       </c>
-      <c r="D30" s="23">
+      <c r="D30" s="22">
         <v>109.9022739</v>
       </c>
       <c r="E30" s="2">
@@ -2407,8 +2407,8 @@
       <c r="B31" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
       <c r="E31" s="2">
         <v>66</v>
       </c>
@@ -2456,10 +2456,10 @@
       <c r="B32" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="23">
+      <c r="C32" s="22">
         <v>-7.2106754000000004</v>
       </c>
-      <c r="D32" s="23">
+      <c r="D32" s="22">
         <v>109.92566720000001</v>
       </c>
       <c r="E32" s="2">
@@ -2509,8 +2509,8 @@
       <c r="B33" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
       <c r="E33" s="2">
         <v>54</v>
       </c>
@@ -2558,10 +2558,10 @@
       <c r="B34" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="23">
+      <c r="C34" s="22">
         <v>-7.2349164000000004</v>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="22">
         <v>109.93564360000001</v>
       </c>
       <c r="E34" s="2">
@@ -2611,8 +2611,8 @@
       <c r="B35" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
       <c r="E35" s="2">
         <v>22</v>
       </c>
@@ -2660,10 +2660,10 @@
       <c r="B36" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="23">
+      <c r="C36" s="22">
         <v>-7.3318916999999999</v>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="22">
         <v>110.029515</v>
       </c>
       <c r="E36" s="2">
@@ -2713,8 +2713,8 @@
       <c r="B37" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
       <c r="E37" s="2">
         <v>70</v>
       </c>
@@ -2762,10 +2762,10 @@
       <c r="B38" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C38" s="25">
+      <c r="C38" s="26">
         <v>-7.3316140000000001</v>
       </c>
-      <c r="D38" s="23">
+      <c r="D38" s="22">
         <v>110.02983039999999</v>
       </c>
       <c r="E38" s="2">
@@ -2815,8 +2815,8 @@
       <c r="B39" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
       <c r="E39" s="2">
         <v>12</v>
       </c>
@@ -2864,10 +2864,10 @@
       <c r="B40" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C40" s="25">
+      <c r="C40" s="26">
         <v>-7.3316140000000001</v>
       </c>
-      <c r="D40" s="23">
+      <c r="D40" s="22">
         <v>110.02983039999999</v>
       </c>
       <c r="E40" s="2">
@@ -2917,8 +2917,8 @@
       <c r="B41" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
       <c r="E41" s="2">
         <v>768</v>
       </c>
@@ -2966,10 +2966,10 @@
       <c r="B42" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C42" s="23">
+      <c r="C42" s="22">
         <v>-7.3343850000000002</v>
       </c>
-      <c r="D42" s="23">
+      <c r="D42" s="22">
         <v>110.031415</v>
       </c>
       <c r="E42" s="2">
@@ -3019,8 +3019,8 @@
       <c r="B43" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="24"/>
-      <c r="D43" s="24"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
       <c r="E43" s="2">
         <v>4</v>
       </c>
@@ -3068,10 +3068,10 @@
       <c r="B44" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C44" s="23">
+      <c r="C44" s="22">
         <v>-7.9071776700000003</v>
       </c>
-      <c r="D44" s="25">
+      <c r="D44" s="26">
         <v>112.92400499999999</v>
       </c>
       <c r="E44" s="2">
@@ -3121,8 +3121,8 @@
       <c r="B45" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C45" s="24"/>
-      <c r="D45" s="24"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
       <c r="E45" s="2">
         <v>27</v>
       </c>
@@ -3170,10 +3170,10 @@
       <c r="B46" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C46" s="23">
+      <c r="C46" s="22">
         <v>-7.9068788000000003</v>
       </c>
-      <c r="D46" s="23">
+      <c r="D46" s="22">
         <v>112.9247951</v>
       </c>
       <c r="E46" s="2">
@@ -3223,8 +3223,8 @@
       <c r="B47" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C47" s="24"/>
-      <c r="D47" s="24"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
       <c r="E47" s="2">
         <v>44</v>
       </c>
@@ -3272,10 +3272,10 @@
       <c r="B48" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="23">
+      <c r="C48" s="22">
         <v>-7.9109334999999996</v>
       </c>
-      <c r="D48" s="23">
+      <c r="D48" s="22">
         <v>112.9053895</v>
       </c>
       <c r="E48" s="2">
@@ -3325,8 +3325,8 @@
       <c r="B49" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C49" s="24"/>
-      <c r="D49" s="24"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="20"/>
       <c r="E49" s="2">
         <v>13</v>
       </c>
@@ -3374,10 +3374,10 @@
       <c r="B50" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C50" s="23">
+      <c r="C50" s="22">
         <v>-7.8936593000000004</v>
       </c>
-      <c r="D50" s="23">
+      <c r="D50" s="22">
         <v>112.9054072</v>
       </c>
       <c r="E50" s="2">
@@ -3427,8 +3427,8 @@
       <c r="B51" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C51" s="24"/>
-      <c r="D51" s="24"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="20"/>
       <c r="E51" s="2">
         <v>24</v>
       </c>
@@ -3476,10 +3476,10 @@
       <c r="B52" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C52" s="23">
+      <c r="C52" s="22">
         <v>-7.8832089999999999</v>
       </c>
-      <c r="D52" s="23">
+      <c r="D52" s="22">
         <v>112.8975631</v>
       </c>
       <c r="E52" s="2">
@@ -3529,8 +3529,8 @@
       <c r="B53" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C53" s="24"/>
-      <c r="D53" s="24"/>
+      <c r="C53" s="20"/>
+      <c r="D53" s="20"/>
       <c r="E53" s="2">
         <v>135</v>
       </c>
@@ -3578,10 +3578,10 @@
       <c r="B54" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C54" s="23">
+      <c r="C54" s="22">
         <v>-7.7639060000000004</v>
       </c>
-      <c r="D54" s="23">
+      <c r="D54" s="22">
         <v>112.89667505</v>
       </c>
       <c r="E54" s="2">
@@ -3631,8 +3631,8 @@
       <c r="B55" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C55" s="24"/>
-      <c r="D55" s="24"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="20"/>
       <c r="E55" s="2">
         <v>120</v>
       </c>
@@ -3680,10 +3680,10 @@
       <c r="B56" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C56" s="23">
+      <c r="C56" s="22">
         <v>-7.8871412999999997</v>
       </c>
-      <c r="D56" s="23">
+      <c r="D56" s="22">
         <v>112.90235730000001</v>
       </c>
       <c r="E56" s="2">
@@ -3733,8 +3733,8 @@
       <c r="B57" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C57" s="24"/>
-      <c r="D57" s="24"/>
+      <c r="C57" s="20"/>
+      <c r="D57" s="20"/>
       <c r="E57" s="2">
         <v>64</v>
       </c>
@@ -3782,10 +3782,10 @@
       <c r="B58" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C58" s="25">
+      <c r="C58" s="26">
         <v>-7.8838473000000002</v>
       </c>
-      <c r="D58" s="26">
+      <c r="D58" s="24">
         <v>112.8924464</v>
       </c>
       <c r="E58" s="2">
@@ -3835,8 +3835,8 @@
       <c r="B59" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C59" s="24"/>
-      <c r="D59" s="27"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="25"/>
       <c r="E59" s="2">
         <v>54</v>
       </c>
@@ -3884,10 +3884,10 @@
       <c r="B60" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C60" s="25">
-        <v>7.8840054999999998</v>
-      </c>
-      <c r="D60" s="25">
+      <c r="C60" s="26">
+        <v>-7.8840054999999998</v>
+      </c>
+      <c r="D60" s="26">
         <v>112.8917843</v>
       </c>
       <c r="E60" s="2">
@@ -3937,8 +3937,8 @@
       <c r="B61" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
+      <c r="C61" s="20"/>
+      <c r="D61" s="20"/>
       <c r="E61" s="2">
         <v>32</v>
       </c>
@@ -3986,10 +3986,10 @@
       <c r="B62" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C62" s="25">
+      <c r="C62" s="26">
         <v>-7.9017467000000003</v>
       </c>
-      <c r="D62" s="25">
+      <c r="D62" s="26">
         <v>112.89530499999999</v>
       </c>
       <c r="E62" s="2">
@@ -4039,8 +4039,8 @@
       <c r="B63" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C63" s="24"/>
-      <c r="D63" s="24"/>
+      <c r="C63" s="20"/>
+      <c r="D63" s="20"/>
       <c r="E63" s="2">
         <v>6</v>
       </c>
@@ -4088,10 +4088,10 @@
       <c r="B64" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C64" s="25">
+      <c r="C64" s="26">
         <v>-7.9018398999999997</v>
       </c>
-      <c r="D64" s="25">
+      <c r="D64" s="26">
         <v>112.8955867</v>
       </c>
       <c r="E64" s="2">
@@ -4141,8 +4141,8 @@
       <c r="B65" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C65" s="24"/>
-      <c r="D65" s="24"/>
+      <c r="C65" s="20"/>
+      <c r="D65" s="20"/>
       <c r="E65" s="2">
         <v>32</v>
       </c>
@@ -4190,10 +4190,10 @@
       <c r="B66" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C66" s="28">
+      <c r="C66" s="19">
         <v>-7.9237320000000002</v>
       </c>
-      <c r="D66" s="28">
+      <c r="D66" s="19">
         <v>112.9939159</v>
       </c>
       <c r="E66" s="2">
@@ -4243,8 +4243,8 @@
       <c r="B67" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C67" s="24"/>
-      <c r="D67" s="24"/>
+      <c r="C67" s="20"/>
+      <c r="D67" s="20"/>
       <c r="E67" s="2">
         <v>0</v>
       </c>
@@ -4292,10 +4292,10 @@
       <c r="B68" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C68" s="28">
+      <c r="C68" s="19">
         <v>-7.9241697999999996</v>
       </c>
-      <c r="D68" s="28">
+      <c r="D68" s="19">
         <v>112.9937937</v>
       </c>
       <c r="E68" s="2">
@@ -4345,8 +4345,8 @@
       <c r="B69" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C69" s="24"/>
-      <c r="D69" s="24"/>
+      <c r="C69" s="20"/>
+      <c r="D69" s="20"/>
       <c r="E69" s="2">
         <v>6</v>
       </c>
@@ -4394,10 +4394,10 @@
       <c r="B70" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C70" s="28">
+      <c r="C70" s="19">
         <v>-7.9232845000000003</v>
       </c>
-      <c r="D70" s="28">
+      <c r="D70" s="19">
         <v>112.99399560000001</v>
       </c>
       <c r="E70" s="2">
@@ -4445,8 +4445,8 @@
       <c r="B71" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C71" s="29"/>
-      <c r="D71" s="29"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
       <c r="E71" s="2">
         <v>30</v>
       </c>
@@ -4492,8 +4492,8 @@
       <c r="B72" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C72" s="29"/>
-      <c r="D72" s="29"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
       <c r="E72" s="2">
         <v>32</v>
       </c>
@@ -4539,8 +4539,8 @@
       <c r="B73" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C73" s="24"/>
-      <c r="D73" s="24"/>
+      <c r="C73" s="20"/>
+      <c r="D73" s="20"/>
       <c r="E73" s="2">
         <v>25</v>
       </c>
@@ -4586,10 +4586,10 @@
       <c r="B74" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C74" s="28">
+      <c r="C74" s="19">
         <v>-7.9249821999999996</v>
       </c>
-      <c r="D74" s="28">
+      <c r="D74" s="19">
         <v>112.9831394</v>
       </c>
       <c r="E74" s="2">
@@ -4637,8 +4637,8 @@
       <c r="B75" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C75" s="29"/>
-      <c r="D75" s="29"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="21"/>
       <c r="E75" s="2">
         <v>30</v>
       </c>
@@ -4684,8 +4684,8 @@
       <c r="B76" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C76" s="29"/>
-      <c r="D76" s="29"/>
+      <c r="C76" s="21"/>
+      <c r="D76" s="21"/>
       <c r="E76" s="2">
         <v>41</v>
       </c>
@@ -4731,8 +4731,8 @@
       <c r="B77" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C77" s="24"/>
-      <c r="D77" s="24"/>
+      <c r="C77" s="20"/>
+      <c r="D77" s="20"/>
       <c r="E77" s="2">
         <v>15</v>
       </c>
@@ -4778,10 +4778,10 @@
       <c r="B78" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C78" s="28">
+      <c r="C78" s="19">
         <v>-7.9251022000000004</v>
       </c>
-      <c r="D78" s="28">
+      <c r="D78" s="19">
         <v>112.9835618</v>
       </c>
       <c r="E78" s="2">
@@ -4829,8 +4829,8 @@
       <c r="B79" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C79" s="29"/>
-      <c r="D79" s="29"/>
+      <c r="C79" s="21"/>
+      <c r="D79" s="21"/>
       <c r="E79" s="2">
         <v>40</v>
       </c>
@@ -4876,8 +4876,8 @@
       <c r="B80" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C80" s="29"/>
-      <c r="D80" s="29"/>
+      <c r="C80" s="21"/>
+      <c r="D80" s="21"/>
       <c r="E80" s="2">
         <v>21</v>
       </c>
@@ -4923,8 +4923,8 @@
       <c r="B81" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C81" s="24"/>
-      <c r="D81" s="24"/>
+      <c r="C81" s="20"/>
+      <c r="D81" s="20"/>
       <c r="E81" s="2">
         <v>30</v>
       </c>
@@ -4970,10 +4970,10 @@
       <c r="B82" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C82" s="28">
+      <c r="C82" s="19">
         <v>-7.9093112000000003</v>
       </c>
-      <c r="D82" s="28">
+      <c r="D82" s="19">
         <v>1129570434</v>
       </c>
       <c r="E82" s="2">
@@ -5023,8 +5023,8 @@
       <c r="B83" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C83" s="24"/>
-      <c r="D83" s="24"/>
+      <c r="C83" s="20"/>
+      <c r="D83" s="20"/>
       <c r="E83" s="2">
         <v>12</v>
       </c>
@@ -5072,10 +5072,10 @@
       <c r="B84" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C84" s="28">
+      <c r="C84" s="19">
         <v>-7.9090024999999997</v>
       </c>
-      <c r="D84" s="28">
+      <c r="D84" s="19">
         <v>1129572636</v>
       </c>
       <c r="E84" s="2">
@@ -5125,8 +5125,8 @@
       <c r="B85" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C85" s="24"/>
-      <c r="D85" s="24"/>
+      <c r="C85" s="20"/>
+      <c r="D85" s="20"/>
       <c r="E85" s="2">
         <v>46</v>
       </c>
@@ -5174,10 +5174,10 @@
       <c r="B86" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C86" s="28">
+      <c r="C86" s="19">
         <v>-7.9245038000000001</v>
       </c>
-      <c r="D86" s="28">
+      <c r="D86" s="19">
         <v>112.99976239999999</v>
       </c>
       <c r="E86" s="2">
@@ -5225,8 +5225,8 @@
       <c r="B87" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C87" s="29"/>
-      <c r="D87" s="29"/>
+      <c r="C87" s="21"/>
+      <c r="D87" s="21"/>
       <c r="E87" s="2">
         <v>36</v>
       </c>
@@ -5272,8 +5272,8 @@
       <c r="B88" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C88" s="29"/>
-      <c r="D88" s="29"/>
+      <c r="C88" s="21"/>
+      <c r="D88" s="21"/>
       <c r="E88" s="2">
         <v>40</v>
       </c>
@@ -5319,8 +5319,8 @@
       <c r="B89" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C89" s="24"/>
-      <c r="D89" s="24"/>
+      <c r="C89" s="20"/>
+      <c r="D89" s="20"/>
       <c r="E89" s="2">
         <v>30</v>
       </c>
@@ -5366,10 +5366,10 @@
       <c r="B90" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C90" s="28">
+      <c r="C90" s="19">
         <v>-7.9168488000000004</v>
       </c>
-      <c r="D90" s="28">
+      <c r="D90" s="19">
         <v>113.0295115</v>
       </c>
       <c r="E90" s="2">
@@ -5415,8 +5415,8 @@
       <c r="B91" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C91" s="29"/>
-      <c r="D91" s="29"/>
+      <c r="C91" s="21"/>
+      <c r="D91" s="21"/>
       <c r="E91" s="2">
         <v>23</v>
       </c>
@@ -5460,8 +5460,8 @@
       <c r="B92" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C92" s="29"/>
-      <c r="D92" s="29"/>
+      <c r="C92" s="21"/>
+      <c r="D92" s="21"/>
       <c r="E92" s="2">
         <v>19</v>
       </c>
@@ -5505,8 +5505,8 @@
       <c r="B93" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C93" s="24"/>
-      <c r="D93" s="24"/>
+      <c r="C93" s="20"/>
+      <c r="D93" s="20"/>
       <c r="E93" s="2">
         <v>20</v>
       </c>
@@ -5550,10 +5550,10 @@
       <c r="B94" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C94" s="28">
+      <c r="C94" s="19">
         <v>-7.9594959999999997</v>
       </c>
-      <c r="D94" s="28">
+      <c r="D94" s="19">
         <v>11308288</v>
       </c>
       <c r="E94" s="2">
@@ -5603,8 +5603,8 @@
       <c r="B95" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C95" s="24"/>
-      <c r="D95" s="24"/>
+      <c r="C95" s="20"/>
+      <c r="D95" s="20"/>
       <c r="E95" s="2">
         <v>15</v>
       </c>
@@ -5652,10 +5652,10 @@
       <c r="B96" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C96" s="28">
+      <c r="C96" s="19">
         <v>-7.9557561999999997</v>
       </c>
-      <c r="D96" s="28">
+      <c r="D96" s="19">
         <v>1130954738</v>
       </c>
       <c r="E96" s="2">
@@ -5705,8 +5705,8 @@
       <c r="B97" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C97" s="24"/>
-      <c r="D97" s="24"/>
+      <c r="C97" s="20"/>
+      <c r="D97" s="20"/>
       <c r="E97" s="2">
         <v>81</v>
       </c>
@@ -5754,10 +5754,10 @@
       <c r="B98" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C98" s="28">
+      <c r="C98" s="19">
         <v>-7.9543477999999999</v>
       </c>
-      <c r="D98" s="28">
+      <c r="D98" s="19">
         <v>113.09633100000001</v>
       </c>
       <c r="E98" s="2">
@@ -5807,8 +5807,8 @@
       <c r="B99" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C99" s="24"/>
-      <c r="D99" s="24"/>
+      <c r="C99" s="20"/>
+      <c r="D99" s="20"/>
       <c r="E99" s="2">
         <v>24</v>
       </c>
@@ -5856,10 +5856,10 @@
       <c r="B100" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C100" s="28">
+      <c r="C100" s="19">
         <v>-8.0308018099999998</v>
       </c>
-      <c r="D100" s="28">
+      <c r="D100" s="19">
         <v>112.28999279999999</v>
       </c>
       <c r="E100" s="2">
@@ -5907,8 +5907,8 @@
       <c r="B101" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C101" s="29"/>
-      <c r="D101" s="29"/>
+      <c r="C101" s="21"/>
+      <c r="D101" s="21"/>
       <c r="E101" s="2">
         <v>21</v>
       </c>
@@ -5954,8 +5954,8 @@
       <c r="B102" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C102" s="29"/>
-      <c r="D102" s="29"/>
+      <c r="C102" s="21"/>
+      <c r="D102" s="21"/>
       <c r="E102" s="2">
         <v>27</v>
       </c>
@@ -6001,8 +6001,8 @@
       <c r="B103" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C103" s="24"/>
-      <c r="D103" s="24"/>
+      <c r="C103" s="20"/>
+      <c r="D103" s="20"/>
       <c r="E103" s="2">
         <v>31</v>
       </c>
@@ -6048,10 +6048,10 @@
       <c r="B104" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C104" s="28">
+      <c r="C104" s="19">
         <v>-7.8917970999999998</v>
       </c>
-      <c r="D104" s="28">
+      <c r="D104" s="19">
         <v>112.36508499999999</v>
       </c>
       <c r="E104" s="2">
@@ -6101,8 +6101,8 @@
       <c r="B105" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C105" s="24"/>
-      <c r="D105" s="24"/>
+      <c r="C105" s="20"/>
+      <c r="D105" s="20"/>
       <c r="E105" s="2">
         <v>128</v>
       </c>
@@ -6150,10 +6150,10 @@
       <c r="B106" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C106" s="28">
+      <c r="C106" s="19">
         <v>-7.8917970999999998</v>
       </c>
-      <c r="D106" s="28">
+      <c r="D106" s="19">
         <v>112.365087</v>
       </c>
       <c r="E106" s="2">
@@ -6203,8 +6203,8 @@
       <c r="B107" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C107" s="24"/>
-      <c r="D107" s="24"/>
+      <c r="C107" s="20"/>
+      <c r="D107" s="20"/>
       <c r="E107" s="2">
         <v>97</v>
       </c>
@@ -6252,10 +6252,10 @@
       <c r="B108" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C108" s="28">
+      <c r="C108" s="19">
         <v>-7.8616799000000004</v>
       </c>
-      <c r="D108" s="28">
+      <c r="D108" s="19">
         <v>112.4612454</v>
       </c>
       <c r="E108" s="4">
@@ -6301,8 +6301,8 @@
       <c r="B109" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C109" s="29"/>
-      <c r="D109" s="29"/>
+      <c r="C109" s="21"/>
+      <c r="D109" s="21"/>
       <c r="E109" s="4">
         <v>29</v>
       </c>
@@ -6346,8 +6346,8 @@
       <c r="B110" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C110" s="29"/>
-      <c r="D110" s="29"/>
+      <c r="C110" s="21"/>
+      <c r="D110" s="21"/>
       <c r="E110" s="4">
         <v>27</v>
       </c>
@@ -6391,8 +6391,8 @@
       <c r="B111" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C111" s="24"/>
-      <c r="D111" s="24"/>
+      <c r="C111" s="20"/>
+      <c r="D111" s="20"/>
       <c r="E111" s="4">
         <v>70</v>
       </c>
@@ -6436,10 +6436,10 @@
       <c r="B112" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C112" s="28">
+      <c r="C112" s="19">
         <v>-7.8564914000000003</v>
       </c>
-      <c r="D112" s="28">
+      <c r="D112" s="19">
         <v>112.4773505</v>
       </c>
       <c r="E112" s="4">
@@ -6485,8 +6485,8 @@
       <c r="B113" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C113" s="29"/>
-      <c r="D113" s="29"/>
+      <c r="C113" s="21"/>
+      <c r="D113" s="21"/>
       <c r="E113" s="4">
         <v>62</v>
       </c>
@@ -6530,8 +6530,8 @@
       <c r="B114" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C114" s="29"/>
-      <c r="D114" s="29"/>
+      <c r="C114" s="21"/>
+      <c r="D114" s="21"/>
       <c r="E114" s="4">
         <v>38</v>
       </c>
@@ -6575,8 +6575,8 @@
       <c r="B115" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C115" s="24"/>
-      <c r="D115" s="24"/>
+      <c r="C115" s="20"/>
+      <c r="D115" s="20"/>
       <c r="E115" s="4">
         <v>44</v>
       </c>
@@ -6620,10 +6620,10 @@
       <c r="B116" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C116" s="28">
+      <c r="C116" s="19">
         <v>-7.7555825</v>
       </c>
-      <c r="D116" s="28">
+      <c r="D116" s="19">
         <v>112.53453690000001</v>
       </c>
       <c r="E116" s="4">
@@ -6671,8 +6671,8 @@
       <c r="B117" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C117" s="29"/>
-      <c r="D117" s="29"/>
+      <c r="C117" s="21"/>
+      <c r="D117" s="21"/>
       <c r="E117" s="4">
         <v>69</v>
       </c>
@@ -6718,8 +6718,8 @@
       <c r="B118" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C118" s="29"/>
-      <c r="D118" s="29"/>
+      <c r="C118" s="21"/>
+      <c r="D118" s="21"/>
       <c r="E118" s="4">
         <v>54</v>
       </c>
@@ -6765,8 +6765,8 @@
       <c r="B119" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C119" s="24"/>
-      <c r="D119" s="24"/>
+      <c r="C119" s="20"/>
+      <c r="D119" s="20"/>
       <c r="E119" s="4">
         <v>52</v>
       </c>
@@ -6812,10 +6812,10 @@
       <c r="B120" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C120" s="28">
+      <c r="C120" s="19">
         <v>-7.7605025999999997</v>
       </c>
-      <c r="D120" s="28">
+      <c r="D120" s="19">
         <v>112.5283429</v>
       </c>
       <c r="E120" s="4">
@@ -6863,8 +6863,8 @@
       <c r="B121" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C121" s="29"/>
-      <c r="D121" s="29"/>
+      <c r="C121" s="21"/>
+      <c r="D121" s="21"/>
       <c r="E121" s="4">
         <v>40</v>
       </c>
@@ -6910,8 +6910,8 @@
       <c r="B122" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C122" s="29"/>
-      <c r="D122" s="29"/>
+      <c r="C122" s="21"/>
+      <c r="D122" s="21"/>
       <c r="E122" s="4">
         <v>24</v>
       </c>
@@ -6957,8 +6957,8 @@
       <c r="B123" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C123" s="24"/>
-      <c r="D123" s="24"/>
+      <c r="C123" s="20"/>
+      <c r="D123" s="20"/>
       <c r="E123" s="4">
         <v>25</v>
       </c>
@@ -7004,10 +7004,10 @@
       <c r="B124" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C124" s="28">
+      <c r="C124" s="19">
         <v>-7.1908266999999997</v>
       </c>
-      <c r="D124" s="28">
+      <c r="D124" s="19">
         <v>107.6129</v>
       </c>
       <c r="E124" s="2">
@@ -7057,8 +7057,8 @@
       <c r="B125" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C125" s="24"/>
-      <c r="D125" s="24"/>
+      <c r="C125" s="20"/>
+      <c r="D125" s="20"/>
       <c r="E125" s="2">
         <v>44</v>
       </c>
@@ -7106,10 +7106,10 @@
       <c r="B126" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C126" s="28">
+      <c r="C126" s="19">
         <v>-7.1865582999999997</v>
       </c>
-      <c r="D126" s="28">
+      <c r="D126" s="19">
         <v>107.6311717</v>
       </c>
       <c r="E126" s="2">
@@ -7159,8 +7159,8 @@
       <c r="B127" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C127" s="24"/>
-      <c r="D127" s="24"/>
+      <c r="C127" s="20"/>
+      <c r="D127" s="20"/>
       <c r="E127" s="2">
         <v>256</v>
       </c>
@@ -7208,10 +7208,10 @@
       <c r="B128" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C128" s="28">
+      <c r="C128" s="19">
         <v>-7.1879999999999997</v>
       </c>
-      <c r="D128" s="28">
+      <c r="D128" s="19">
         <v>107.6254533</v>
       </c>
       <c r="E128" s="2">
@@ -7261,8 +7261,8 @@
       <c r="B129" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C129" s="24"/>
-      <c r="D129" s="24"/>
+      <c r="C129" s="20"/>
+      <c r="D129" s="20"/>
       <c r="E129" s="2">
         <v>371</v>
       </c>
@@ -7310,10 +7310,10 @@
       <c r="B130" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C130" s="28">
+      <c r="C130" s="19">
         <v>-7.1857772999999998</v>
       </c>
-      <c r="D130" s="28">
+      <c r="D130" s="19">
         <v>107.6157188</v>
       </c>
       <c r="E130" s="2">
@@ -7363,8 +7363,8 @@
       <c r="B131" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C131" s="24"/>
-      <c r="D131" s="24"/>
+      <c r="C131" s="20"/>
+      <c r="D131" s="20"/>
       <c r="E131" s="2">
         <v>72</v>
       </c>
@@ -7412,10 +7412,10 @@
       <c r="B132" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C132" s="28">
+      <c r="C132" s="19">
         <v>-7.2059867999999998</v>
       </c>
-      <c r="D132" s="28">
+      <c r="D132" s="19">
         <v>107.6042921</v>
       </c>
       <c r="E132" s="2">
@@ -7465,8 +7465,8 @@
       <c r="B133" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C133" s="24"/>
-      <c r="D133" s="24"/>
+      <c r="C133" s="20"/>
+      <c r="D133" s="20"/>
       <c r="E133" s="2">
         <v>33</v>
       </c>
@@ -7663,10 +7663,10 @@
       <c r="B137" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C137" s="28">
+      <c r="C137" s="19">
         <v>-7.3651612999999996</v>
       </c>
-      <c r="D137" s="28">
+      <c r="D137" s="19">
         <v>107.7884202</v>
       </c>
       <c r="E137" s="2">
@@ -7716,8 +7716,8 @@
       <c r="B138" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C138" s="24"/>
-      <c r="D138" s="24"/>
+      <c r="C138" s="20"/>
+      <c r="D138" s="20"/>
       <c r="E138" s="2">
         <v>21</v>
       </c>
@@ -7765,10 +7765,10 @@
       <c r="B139" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C139" s="28">
+      <c r="C139" s="19">
         <v>-7.3652267</v>
       </c>
-      <c r="D139" s="28">
+      <c r="D139" s="19">
         <v>107.7897238</v>
       </c>
       <c r="E139" s="2">
@@ -7818,8 +7818,8 @@
       <c r="B140" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C140" s="24"/>
-      <c r="D140" s="24"/>
+      <c r="C140" s="20"/>
+      <c r="D140" s="20"/>
       <c r="E140" s="2">
         <v>26</v>
       </c>
@@ -7867,10 +7867,10 @@
       <c r="B141" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C141" s="28">
+      <c r="C141" s="19">
         <v>-7.3683959000000003</v>
       </c>
-      <c r="D141" s="28">
+      <c r="D141" s="19">
         <v>107.7638857</v>
       </c>
       <c r="E141" s="2">
@@ -7920,8 +7920,8 @@
       <c r="B142" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C142" s="24"/>
-      <c r="D142" s="24"/>
+      <c r="C142" s="20"/>
+      <c r="D142" s="20"/>
       <c r="E142" s="2">
         <v>182</v>
       </c>
@@ -7969,10 +7969,10 @@
       <c r="B143" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C143" s="28">
+      <c r="C143" s="19">
         <v>-7.3569129000000002</v>
       </c>
-      <c r="D143" s="28">
+      <c r="D143" s="19">
         <v>107.75423410000001</v>
       </c>
       <c r="E143" s="2">
@@ -8022,8 +8022,8 @@
       <c r="B144" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C144" s="24"/>
-      <c r="D144" s="24"/>
+      <c r="C144" s="20"/>
+      <c r="D144" s="20"/>
       <c r="E144" s="2">
         <v>75</v>
       </c>
@@ -8071,10 +8071,10 @@
       <c r="B145" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C145" s="30">
+      <c r="C145" s="23">
         <v>-7.3628650000000002</v>
       </c>
-      <c r="D145" s="30">
+      <c r="D145" s="23">
         <v>107.78986329999999</v>
       </c>
       <c r="E145" s="2">
@@ -8124,8 +8124,8 @@
       <c r="B146" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C146" s="24"/>
-      <c r="D146" s="24"/>
+      <c r="C146" s="20"/>
+      <c r="D146" s="20"/>
       <c r="E146" s="2">
         <v>32</v>
       </c>
@@ -8173,10 +8173,10 @@
       <c r="B147" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C147" s="30">
+      <c r="C147" s="23">
         <v>-7.3721291000000004</v>
       </c>
-      <c r="D147" s="30">
+      <c r="D147" s="23">
         <v>107.7540844</v>
       </c>
       <c r="E147" s="2">
@@ -8226,8 +8226,8 @@
       <c r="B148" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C148" s="24"/>
-      <c r="D148" s="24"/>
+      <c r="C148" s="20"/>
+      <c r="D148" s="20"/>
       <c r="E148" s="2">
         <v>48</v>
       </c>
@@ -8275,10 +8275,10 @@
       <c r="B149" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C149" s="28">
+      <c r="C149" s="19">
         <v>-7.2231167000000003</v>
       </c>
-      <c r="D149" s="28">
+      <c r="D149" s="19">
         <v>107.741305</v>
       </c>
       <c r="E149" s="2">
@@ -8328,8 +8328,8 @@
       <c r="B150" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C150" s="24"/>
-      <c r="D150" s="24"/>
+      <c r="C150" s="20"/>
+      <c r="D150" s="20"/>
       <c r="E150" s="2">
         <v>7</v>
       </c>
@@ -8377,10 +8377,10 @@
       <c r="B151" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C151" s="28">
+      <c r="C151" s="19">
         <v>-7.2199381000000002</v>
       </c>
-      <c r="D151" s="28">
+      <c r="D151" s="19">
         <v>107.7428596</v>
       </c>
       <c r="E151" s="2">
@@ -8430,8 +8430,8 @@
       <c r="B152" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C152" s="24"/>
-      <c r="D152" s="24"/>
+      <c r="C152" s="20"/>
+      <c r="D152" s="20"/>
       <c r="E152" s="2">
         <v>72</v>
       </c>
@@ -8479,10 +8479,10 @@
       <c r="B153" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C153" s="30">
+      <c r="C153" s="23">
         <v>-7.2169850000000002</v>
       </c>
-      <c r="D153" s="30">
+      <c r="D153" s="23">
         <v>107.7462417</v>
       </c>
       <c r="E153" s="2">
@@ -8532,8 +8532,8 @@
       <c r="B154" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C154" s="24"/>
-      <c r="D154" s="24"/>
+      <c r="C154" s="20"/>
+      <c r="D154" s="20"/>
       <c r="E154" s="2">
         <v>62</v>
       </c>
@@ -8581,10 +8581,10 @@
       <c r="B155" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C155" s="23">
+      <c r="C155" s="22">
         <v>-7.2656055000000004</v>
       </c>
-      <c r="D155" s="23">
+      <c r="D155" s="22">
         <v>108.10440699999999</v>
       </c>
       <c r="E155" s="2">
@@ -8630,8 +8630,8 @@
       <c r="B156" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C156" s="29"/>
-      <c r="D156" s="29"/>
+      <c r="C156" s="21"/>
+      <c r="D156" s="21"/>
       <c r="E156" s="2">
         <v>54</v>
       </c>
@@ -8675,8 +8675,8 @@
       <c r="B157" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C157" s="29"/>
-      <c r="D157" s="29"/>
+      <c r="C157" s="21"/>
+      <c r="D157" s="21"/>
       <c r="E157" s="2">
         <v>40</v>
       </c>
@@ -8720,8 +8720,8 @@
       <c r="B158" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C158" s="24"/>
-      <c r="D158" s="24"/>
+      <c r="C158" s="20"/>
+      <c r="D158" s="20"/>
       <c r="E158" s="2">
         <v>28</v>
       </c>
@@ -8765,10 +8765,10 @@
       <c r="B159" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C159" s="23">
+      <c r="C159" s="22">
         <v>-7.2645523000000001</v>
       </c>
-      <c r="D159" s="23">
+      <c r="D159" s="22">
         <v>108.10110426999999</v>
       </c>
       <c r="E159" s="2">
@@ -8814,8 +8814,8 @@
       <c r="B160" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C160" s="29"/>
-      <c r="D160" s="29"/>
+      <c r="C160" s="21"/>
+      <c r="D160" s="21"/>
       <c r="E160" s="2">
         <v>29</v>
       </c>
@@ -8859,8 +8859,8 @@
       <c r="B161" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C161" s="29"/>
-      <c r="D161" s="29"/>
+      <c r="C161" s="21"/>
+      <c r="D161" s="21"/>
       <c r="E161" s="2">
         <v>13</v>
       </c>
@@ -8904,8 +8904,8 @@
       <c r="B162" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C162" s="24"/>
-      <c r="D162" s="24"/>
+      <c r="C162" s="20"/>
+      <c r="D162" s="20"/>
       <c r="E162" s="2">
         <v>58</v>
       </c>
@@ -8949,10 +8949,10 @@
       <c r="B163" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C163" s="28">
+      <c r="C163" s="19">
         <v>-8.0253496999999996</v>
       </c>
-      <c r="D163" s="28">
+      <c r="D163" s="19">
         <v>110.33660209999999</v>
       </c>
       <c r="E163" s="2">
@@ -9000,8 +9000,8 @@
       <c r="B164" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C164" s="29"/>
-      <c r="D164" s="29"/>
+      <c r="C164" s="21"/>
+      <c r="D164" s="21"/>
       <c r="E164" s="2">
         <v>582</v>
       </c>
@@ -9047,8 +9047,8 @@
       <c r="B165" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C165" s="29"/>
-      <c r="D165" s="29"/>
+      <c r="C165" s="21"/>
+      <c r="D165" s="21"/>
       <c r="E165" s="2">
         <v>505</v>
       </c>
@@ -9094,8 +9094,8 @@
       <c r="B166" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C166" s="24"/>
-      <c r="D166" s="24"/>
+      <c r="C166" s="20"/>
+      <c r="D166" s="20"/>
       <c r="E166" s="2">
         <v>685</v>
       </c>
@@ -9141,10 +9141,10 @@
       <c r="B167" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C167" s="28">
+      <c r="C167" s="19">
         <v>-8.0256383000000007</v>
       </c>
-      <c r="D167" s="28">
+      <c r="D167" s="19">
         <v>110.3371807</v>
       </c>
       <c r="E167" s="2">
@@ -9192,8 +9192,8 @@
       <c r="B168" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C168" s="29"/>
-      <c r="D168" s="29"/>
+      <c r="C168" s="21"/>
+      <c r="D168" s="21"/>
       <c r="E168" s="2">
         <v>185</v>
       </c>
@@ -9239,8 +9239,8 @@
       <c r="B169" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C169" s="29"/>
-      <c r="D169" s="29"/>
+      <c r="C169" s="21"/>
+      <c r="D169" s="21"/>
       <c r="E169" s="2">
         <v>338</v>
       </c>
@@ -9286,8 +9286,8 @@
       <c r="B170" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C170" s="24"/>
-      <c r="D170" s="24"/>
+      <c r="C170" s="20"/>
+      <c r="D170" s="20"/>
       <c r="E170" s="2">
         <v>327</v>
       </c>
@@ -9333,10 +9333,10 @@
       <c r="B171" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C171" s="28">
+      <c r="C171" s="19">
         <v>-8.0248114000000008</v>
       </c>
-      <c r="D171" s="28">
+      <c r="D171" s="19">
         <v>110.3382988</v>
       </c>
       <c r="E171" s="2">
@@ -9384,8 +9384,8 @@
       <c r="B172" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C172" s="29"/>
-      <c r="D172" s="29"/>
+      <c r="C172" s="21"/>
+      <c r="D172" s="21"/>
       <c r="E172" s="2">
         <v>124</v>
       </c>
@@ -9431,8 +9431,8 @@
       <c r="B173" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C173" s="29"/>
-      <c r="D173" s="29"/>
+      <c r="C173" s="21"/>
+      <c r="D173" s="21"/>
       <c r="E173" s="2">
         <v>89</v>
       </c>
@@ -9478,8 +9478,8 @@
       <c r="B174" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C174" s="24"/>
-      <c r="D174" s="24"/>
+      <c r="C174" s="20"/>
+      <c r="D174" s="20"/>
       <c r="E174" s="2">
         <v>92</v>
       </c>
@@ -9525,10 +9525,10 @@
       <c r="B175" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C175" s="28">
+      <c r="C175" s="19">
         <v>-7.4981251000000002</v>
       </c>
-      <c r="D175" s="28">
+      <c r="D175" s="19">
         <v>110.32802390000001</v>
       </c>
       <c r="E175" s="2">
@@ -9574,8 +9574,8 @@
       <c r="B176" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C176" s="24"/>
-      <c r="D176" s="24"/>
+      <c r="C176" s="20"/>
+      <c r="D176" s="20"/>
       <c r="E176" s="2">
         <v>31</v>
       </c>
@@ -9619,10 +9619,10 @@
       <c r="B177" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C177" s="28">
+      <c r="C177" s="19">
         <v>-7.4827136000000003</v>
       </c>
-      <c r="D177" s="28">
+      <c r="D177" s="19">
         <v>110.38781299999999</v>
       </c>
       <c r="E177" s="2">
@@ -9668,8 +9668,8 @@
       <c r="B178" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C178" s="24"/>
-      <c r="D178" s="24"/>
+      <c r="C178" s="20"/>
+      <c r="D178" s="20"/>
       <c r="E178" s="2">
         <v>31</v>
       </c>
@@ -9713,10 +9713,10 @@
       <c r="B179" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C179" s="28">
+      <c r="C179" s="19">
         <v>-7.3774337499999998</v>
       </c>
-      <c r="D179" s="28">
+      <c r="D179" s="19">
         <v>110.34128370000001</v>
       </c>
       <c r="E179" s="2">
@@ -9762,8 +9762,8 @@
       <c r="B180" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C180" s="24"/>
-      <c r="D180" s="24"/>
+      <c r="C180" s="20"/>
+      <c r="D180" s="20"/>
       <c r="E180" s="2">
         <v>256</v>
       </c>
@@ -10478,16 +10478,120 @@
     </row>
   </sheetData>
   <mergeCells count="138">
-    <mergeCell ref="C179:C180"/>
-    <mergeCell ref="D175:D176"/>
-    <mergeCell ref="D177:D178"/>
-    <mergeCell ref="D179:D180"/>
-    <mergeCell ref="C171:C174"/>
-    <mergeCell ref="D163:D166"/>
-    <mergeCell ref="D167:D170"/>
-    <mergeCell ref="D171:D174"/>
-    <mergeCell ref="C175:C176"/>
-    <mergeCell ref="C177:C178"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="D12:D15"/>
+    <mergeCell ref="C16:C19"/>
+    <mergeCell ref="D16:D19"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="D20:D23"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C74:C77"/>
+    <mergeCell ref="D74:D77"/>
+    <mergeCell ref="C78:C81"/>
+    <mergeCell ref="D78:D81"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="C70:C73"/>
+    <mergeCell ref="D70:D73"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="D98:D99"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="D86:D89"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="C108:C111"/>
+    <mergeCell ref="C112:C115"/>
+    <mergeCell ref="D108:D111"/>
+    <mergeCell ref="D112:D115"/>
+    <mergeCell ref="C116:C119"/>
+    <mergeCell ref="D116:D119"/>
+    <mergeCell ref="C100:C103"/>
+    <mergeCell ref="D100:D103"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="C120:C123"/>
+    <mergeCell ref="D120:D123"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="C126:C127"/>
+    <mergeCell ref="C128:C129"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="D124:D125"/>
+    <mergeCell ref="D126:D127"/>
+    <mergeCell ref="D128:D129"/>
+    <mergeCell ref="D130:D131"/>
+    <mergeCell ref="C141:C142"/>
+    <mergeCell ref="D141:D142"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="D143:D144"/>
+    <mergeCell ref="C145:C146"/>
+    <mergeCell ref="D145:D146"/>
+    <mergeCell ref="C132:C133"/>
+    <mergeCell ref="D132:D133"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="C139:C140"/>
+    <mergeCell ref="D137:D138"/>
+    <mergeCell ref="D139:D140"/>
     <mergeCell ref="C155:C158"/>
     <mergeCell ref="C159:C162"/>
     <mergeCell ref="D155:D158"/>
@@ -10502,120 +10606,16 @@
     <mergeCell ref="D149:D150"/>
     <mergeCell ref="D151:D152"/>
     <mergeCell ref="D153:D154"/>
-    <mergeCell ref="C141:C142"/>
-    <mergeCell ref="D141:D142"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="D143:D144"/>
-    <mergeCell ref="C145:C146"/>
-    <mergeCell ref="D145:D146"/>
-    <mergeCell ref="C132:C133"/>
-    <mergeCell ref="D132:D133"/>
-    <mergeCell ref="C137:C138"/>
-    <mergeCell ref="C139:C140"/>
-    <mergeCell ref="D137:D138"/>
-    <mergeCell ref="D139:D140"/>
-    <mergeCell ref="C120:C123"/>
-    <mergeCell ref="D120:D123"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="C126:C127"/>
-    <mergeCell ref="C128:C129"/>
-    <mergeCell ref="C130:C131"/>
-    <mergeCell ref="D124:D125"/>
-    <mergeCell ref="D126:D127"/>
-    <mergeCell ref="D128:D129"/>
-    <mergeCell ref="D130:D131"/>
-    <mergeCell ref="C108:C111"/>
-    <mergeCell ref="C112:C115"/>
-    <mergeCell ref="D108:D111"/>
-    <mergeCell ref="D112:D115"/>
-    <mergeCell ref="C116:C119"/>
-    <mergeCell ref="D116:D119"/>
-    <mergeCell ref="C100:C103"/>
-    <mergeCell ref="D100:D103"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="D98:D99"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="C86:C89"/>
-    <mergeCell ref="D86:D89"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="C74:C77"/>
-    <mergeCell ref="D74:D77"/>
-    <mergeCell ref="C78:C81"/>
-    <mergeCell ref="D78:D81"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="C70:C73"/>
-    <mergeCell ref="D70:D73"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="C20:C23"/>
-    <mergeCell ref="D20:D23"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="D12:D15"/>
-    <mergeCell ref="C16:C19"/>
-    <mergeCell ref="D16:D19"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="C179:C180"/>
+    <mergeCell ref="D175:D176"/>
+    <mergeCell ref="D177:D178"/>
+    <mergeCell ref="D179:D180"/>
+    <mergeCell ref="C171:C174"/>
+    <mergeCell ref="D163:D166"/>
+    <mergeCell ref="D167:D170"/>
+    <mergeCell ref="D171:D174"/>
+    <mergeCell ref="C175:C176"/>
+    <mergeCell ref="C177:C178"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
